--- a/data/trans_bre/P1421-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1421-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 7,17</t>
+          <t>0,46; 7,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,54</t>
+          <t>3,67; 9,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,36</t>
+          <t>-1,92; 3,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,28</t>
+          <t>1,5; 7,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 299,73</t>
+          <t>2,97; 326,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>113,2; —</t>
+          <t>119,93; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,15; 164,92</t>
+          <t>-49,28; 188,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,71; 177,41</t>
+          <t>21,69; 185,97</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,43</t>
+          <t>7,46</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>219,59%</t>
+          <t>225,42%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,02</t>
+          <t>2,72; 8,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,68</t>
+          <t>1,3; 6,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,15</t>
+          <t>2,15; 7,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 10,61</t>
+          <t>4,74; 10,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,5; 643,42</t>
+          <t>69,5; 689,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,97; 1836,72</t>
+          <t>45,89; 1762,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>85,78; 2629,95</t>
+          <t>81,78; 2779,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,43; 528,73</t>
+          <t>91,96; 471,19</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,92</t>
+          <t>9,59</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>356,83%</t>
+          <t>203,76%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,2</t>
+          <t>0,76; 9,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,9</t>
+          <t>1,56; 8,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 11,64</t>
+          <t>2,9; 12,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 16,77</t>
+          <t>4,77; 14,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,31; 539,86</t>
+          <t>10,72; 473,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80,85; 1153,68</t>
+          <t>68,33; 1008,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>136,28; 3306,28</t>
+          <t>107,12; 2843,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>131,47; 1441,73</t>
+          <t>67,13; 441,09</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,67</t>
+          <t>7,53</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>166,0%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 6,18</t>
+          <t>2,12; 6,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,53</t>
+          <t>2,06; 5,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,16</t>
+          <t>2,72; 5,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 8,15</t>
+          <t>5,15; 10,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,8; 348,95</t>
+          <t>65,87; 343,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,78; 551,05</t>
+          <t>103,04; 610,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>201,79; 1202,42</t>
+          <t>173,93; 1203,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 190,73</t>
+          <t>88,06; 272,27</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,81</t>
+          <t>8,4</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>125,22%</t>
+          <t>171,38%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 5,56</t>
+          <t>0,34; 5,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,73</t>
+          <t>3,36; 7,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,28</t>
+          <t>2,72; 7,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,12; 10,34</t>
+          <t>5,6; 11,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 444,18</t>
+          <t>1,75; 418,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>154,68; 1459,33</t>
+          <t>146,0; 1319,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,75; 435,87</t>
+          <t>71,57; 461,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,59; 281,19</t>
+          <t>76,58; 329,73</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>212,02%</t>
+          <t>189,92%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,07</t>
+          <t>1,85; 5,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,64</t>
+          <t>0,92; 4,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,75</t>
+          <t>2,41; 5,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,99</t>
+          <t>1,26; 8,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,56; 1586,8</t>
+          <t>52,08; 1596,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,22; 1277,13</t>
+          <t>23,17; 1440,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,06; —</t>
+          <t>79,14; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,38; 781,53</t>
+          <t>10,56; 718,33</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>6,77</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>143,17%</t>
+          <t>153,13%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,29</t>
+          <t>2,32; 4,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,99</t>
+          <t>3,39; 5,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,02</t>
+          <t>3,17; 4,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,76</t>
+          <t>5,61; 7,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,22; 213,06</t>
+          <t>81,95; 221,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>214,09; 522,08</t>
+          <t>220,78; 539,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>181,95; 435,42</t>
+          <t>178,76; 449,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>88,49; 220,85</t>
+          <t>111,08; 201,35</t>
         </is>
       </c>
     </row>
